--- a/PROYECTO_CIGARS_CUBA_2027/09_RESEARCH/Source Register.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/09_RESEARCH/Source Register.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="268">
   <si>
     <t xml:space="preserve">Registro de fuentes — consulta 10/10/2026</t>
   </si>
@@ -698,6 +698,42 @@
   </si>
   <si>
     <t xml:space="preserve">La revisión de la Directiva sigue en el Consejo en agosto de 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habanos / Cigars-Connect — fallecimiento de Arnaldo Vichot, ex maestro ligador de Partagás (24/02/2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.habanos.com/en/news/heartfelt-condolences/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Posible asociación del nombre ARNALDO con una figura conocida del sector; no se halló marca de puros «Arnaldo».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habanos — marca Vegas Robaina (creada en 1997)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.habanos.com/en/the-habanos-brands-academia/vegas-robaina-brand/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marca con nombre de un veguero propiedad de Habanos S.A.: precedente de titularidad estatal de una marca de nombre propio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justia — marcas de GRYSON NV (ARLONDO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://trademark.justia.com/owners/gryson-naamloze-vennootschap-1326237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marca de tabaco ARLONDO: analizar riesgo de confusión con ARNALDO.</t>
   </si>
   <si>
     <t xml:space="preserve">N01</t>
@@ -1188,7 +1224,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -2347,13 +2383,13 @@
         <v>228</v>
       </c>
       <c r="D53" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>230</v>
-      </c>
       <c r="F53" s="4" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>15</v>
@@ -2361,42 +2397,42 @@
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="C54" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="D54" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="E54" s="4" t="s">
+      <c r="F54" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="B55" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="C55" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="D55" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>20</v>
@@ -2407,16 +2443,16 @@
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="C56" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="D56" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>242</v>
@@ -2428,7 +2464,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
         <v>243</v>
       </c>
@@ -2439,7 +2475,7 @@
         <v>245</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>246</v>
@@ -2451,7 +2487,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
         <v>247</v>
       </c>
@@ -2462,7 +2498,7 @@
         <v>249</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>250</v>
@@ -2474,7 +2510,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
         <v>251</v>
       </c>
@@ -2485,15 +2521,84 @@
         <v>253</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>254</v>
       </c>
       <c r="F59" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="B60" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="G62" s="4" t="s">
         <v>15</v>
       </c>
     </row>

--- a/PROYECTO_CIGARS_CUBA_2027/09_RESEARCH/Source Register.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/09_RESEARCH/Source Register.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="282">
   <si>
     <t xml:space="preserve">Registro de fuentes — consulta 10/10/2026</t>
   </si>
@@ -734,6 +734,48 @@
   </si>
   <si>
     <t xml:space="preserve">Marca de tabaco ARLONDO: analizar riesgo de confusión con ARNALDO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Objective — «Los estancos descienden un 3% en diez años» (17/02/2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://theobjective.com/sociedad/2025-02-17/estancos-diez-anos-fumadores-diarios-9/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secundaria (cita datos oficiales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.858 licencias de expendeduría en 2024 (13.287 en 2015). Otra cifra de 16.049 (prensa, 2023) no es coherente con el resto y no se usa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Halfwheel — Habanos S.A. reports $827 million in revenue for 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://halfwheel.com/habanos-s-a-reports-827-million-in-revenue-for-2024-a-14-7-percent-increase/447655/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirma 827 M USD en 2024; calcula +14,7% frente al +16% que comunica la compañía. Mercados: China, España, Suiza, Reino Unido, Alemania; Europa 54%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diario de Cuba / Cigars-Connect / Nicotine Insider — Tabacalera bajo supervisión del Tesoro tras las sanciones UE a Chen Zhi (ago.–sep. 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cigars-connect.com/en/tabacalera-placed-under-spanish-treasury-oversight-following-eu-sanctions-against-chen-zhi/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secundaria (varias fuentes coincidentes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UE sanciona a Chen Zhi y Prince Holding Group (30/07/2026); Chen Zhi controlaba indirectamente el 57,1% de Allied Cigar; Tabacalera (controla ITI Cigars, 50% de Habanos S.A.) opera con cuentas bloqueadas y necesita autorización del Tesoro para pagar; su CEO comunicó que la empresa está sujeta a las sanciones. Las autoridades no lo han confirmado públicamente.</t>
   </si>
   <si>
     <t xml:space="preserve">N01</t>
@@ -1224,7 +1266,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -2475,19 +2517,19 @@
         <v>245</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>241</v>
+        <v>12</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>246</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
         <v>247</v>
       </c>
@@ -2498,10 +2540,10 @@
         <v>249</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>20</v>
@@ -2512,19 +2554,19 @@
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>20</v>
@@ -2533,21 +2575,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>241</v>
-      </c>
       <c r="E60" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>20</v>
@@ -2556,21 +2598,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>20</v>
@@ -2579,26 +2621,95 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>267</v>
+        <v>20</v>
       </c>
       <c r="G62" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G65" s="4" t="s">
         <v>15</v>
       </c>
     </row>

--- a/PROYECTO_CIGARS_CUBA_2027/09_RESEARCH/Source Register.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/09_RESEARCH/Source Register.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="299">
   <si>
     <t xml:space="preserve">Registro de fuentes — consulta 10/10/2026</t>
   </si>
@@ -761,6 +761,57 @@
   </si>
   <si>
     <t xml:space="preserve">Confirma 827 M USD en 2024; calcula +14,7% frente al +16% que comunica la compañía. Mercados: China, España, Suiza, Reino Unido, Alemania; Europa 54%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wikipedia — Cigar band</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/Cigar_band</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se atribuye a Gustave Bock, fabricante en Cuba en el siglo XIX, la invención de la anilla: anillas de papel con su firma para distinguir sus puros de exportación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habanos S.A. — Glossary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.habanos.com/en/glossary/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anilla: término cubano para la vitola de papel; habilitaciones: decoraciones de la caja, cada una con su nombre tradicional, aplicadas a mano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cohiba Atmosphere — Dressing the cigar box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://cohibaatmosphere.com.my/dressing-the-cigar-box/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secundaria (red de Habanos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vista (imagen superior que celebra la marca), bofetón o filete (hoja protectora decorada), larguero (tira de los lados largos con la marca) y costero (tira de los lados cortos con la vitola).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cigar Aficionado — Habanos S.A. (ficha de la compañía)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cigaraficionado.com/company/habanos-s-a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolívar (creada en 1902): la imagen de su epónimo, Simón Bolívar, forma parte de la marca.</t>
   </si>
   <si>
     <t xml:space="preserve">S54</t>
@@ -1266,7 +1317,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -2529,7 +2580,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
         <v>247</v>
       </c>
@@ -2540,10 +2591,10 @@
         <v>249</v>
       </c>
       <c r="D58" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>20</v>
@@ -2554,22 +2605,22 @@
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="C59" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="D59" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>256</v>
-      </c>
       <c r="F59" s="4" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>15</v>
@@ -2577,62 +2628,62 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="D60" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="E60" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="E60" s="4" t="s">
+      <c r="F60" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="F60" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
+      <c r="B61" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="C61" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="D61" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="E61" s="4" t="s">
+      <c r="F61" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
+      <c r="B62" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="C62" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="D62" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>255</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>268</v>
@@ -2644,7 +2695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
         <v>269</v>
       </c>
@@ -2655,10 +2706,10 @@
         <v>271</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>20</v>
@@ -2669,19 +2720,19 @@
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>20</v>
@@ -2690,26 +2741,118 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>281</v>
+        <v>20</v>
       </c>
       <c r="G65" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="G69" s="4" t="s">
         <v>15</v>
       </c>
     </row>

--- a/PROYECTO_CIGARS_CUBA_2027/09_RESEARCH/Source Register.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/09_RESEARCH/Source Register.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="311">
   <si>
     <t xml:space="preserve">Registro de fuentes — consulta 10/10/2026</t>
   </si>
@@ -812,6 +812,42 @@
   </si>
   <si>
     <t xml:space="preserve">Bolívar (creada en 1902): la imagen de su epónimo, Simón Bolívar, forma parte de la marca.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cigar Aficionado — How to spot a fake Hoyo de Monterrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cigaraficionado.com/article/how-to-spot-a-fake-hoyo-de-monterrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anilla estándar de Hoyo de Monterrey: mayoritariamente blanca, con un logotipo rojo central y el nombre en letras blancas; la línea Epicure añade una segunda anilla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simply Cigars — Montecristo 80th anniversary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.simplycigars.co.uk/guide/montecristo-80th-anniversary-cubas-best-selling-brand-1907/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anilla de Montecristo: campo marrón con filigrana de oro y bordes blancos; la flor de lis central va en relieve de oro desde 2013.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JJ Fox — 1935, the year of Montecristo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jjfox.co.uk/blog/cigar-brands/1935-the-year-of-montecristo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montecristo nace en 1935 (Alonso Menéndez, fábrica Particulares); su emblema es un triángulo de espadas en torno a una flor de lis.</t>
   </si>
   <si>
     <t xml:space="preserve">S54</t>
@@ -1317,7 +1353,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -2672,7 +2708,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
         <v>264</v>
       </c>
@@ -2683,10 +2719,10 @@
         <v>266</v>
       </c>
       <c r="D62" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>20</v>
@@ -2697,19 +2733,19 @@
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="C63" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="D63" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>273</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>20</v>
@@ -2720,42 +2756,42 @@
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="D64" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="F64" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="E64" s="4" t="s">
+      <c r="B65" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
+      <c r="C65" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="D65" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="E65" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>281</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>20</v>
@@ -2766,16 +2802,16 @@
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B66" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="C66" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="D66" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>285</v>
@@ -2787,7 +2823,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
         <v>286</v>
       </c>
@@ -2798,7 +2834,7 @@
         <v>288</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>289</v>
@@ -2810,7 +2846,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
         <v>290</v>
       </c>
@@ -2821,7 +2857,7 @@
         <v>292</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>293</v>
@@ -2833,7 +2869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
         <v>294</v>
       </c>
@@ -2844,15 +2880,84 @@
         <v>296</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>297</v>
       </c>
       <c r="F69" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="B70" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>15</v>
       </c>
     </row>

--- a/PROYECTO_CIGARS_CUBA_2027/09_RESEARCH/Source Register.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/09_RESEARCH/Source Register.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="315">
   <si>
     <t xml:space="preserve">Registro de fuentes — consulta 10/10/2026</t>
   </si>
@@ -709,7 +709,7 @@
     <t xml:space="preserve">https://www.habanos.com/en/news/heartfelt-condolences/</t>
   </si>
   <si>
-    <t xml:space="preserve">Posible asociación del nombre ARNALDO con una figura conocida del sector; no se halló marca de puros «Arnaldo».</t>
+    <t xml:space="preserve">Posible asociación del nombre de pila con una figura conocida del sector, atenuada al llevar la marca el apellido (ARNALDO VALLÉS); no se halló marca de puros «Arnaldo».</t>
   </si>
   <si>
     <t xml:space="preserve">S50</t>
@@ -733,7 +733,7 @@
     <t xml:space="preserve">https://trademark.justia.com/owners/gryson-naamloze-vennootschap-1326237</t>
   </si>
   <si>
-    <t xml:space="preserve">Marca de tabaco ARLONDO: analizar riesgo de confusión con ARNALDO.</t>
+    <t xml:space="preserve">Marca de tabaco ARLONDO: analizar riesgo de confusión con ARNALDO VALLÉS.</t>
   </si>
   <si>
     <t xml:space="preserve">S52</t>
@@ -848,6 +848,18 @@
   </si>
   <si>
     <t xml:space="preserve">Montecristo nace en 1935 (Alonso Menéndez, fábrica Particulares); su emblema es un triángulo de espadas en torno a una flor de lis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justia — DON VALLES (DONVALLESCIGARS, LLC), marca de EE. UU. para puros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://trademark.justia.com/866/60/don-86660716.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marca DON VALLES registrada en EE. UU. (5/4/2016) para puros: analizar riesgo de confusión con ARNALDO VALLÉS en el informe de registrabilidad.</t>
   </si>
   <si>
     <t xml:space="preserve">S54</t>
@@ -1353,7 +1365,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -2777,7 +2789,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
         <v>276</v>
       </c>
@@ -2788,33 +2800,33 @@
         <v>278</v>
       </c>
       <c r="D65" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="F65" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+      <c r="B66" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="C66" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="D66" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="E66" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>285</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>20</v>
@@ -2825,16 +2837,16 @@
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="C67" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="D67" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>289</v>
@@ -2846,7 +2858,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
         <v>290</v>
       </c>
@@ -2857,7 +2869,7 @@
         <v>292</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>293</v>
@@ -2869,7 +2881,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
         <v>294</v>
       </c>
@@ -2880,7 +2892,7 @@
         <v>296</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>297</v>
@@ -2892,7 +2904,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
         <v>298</v>
       </c>
@@ -2903,7 +2915,7 @@
         <v>300</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>301</v>
@@ -2915,7 +2927,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
         <v>302</v>
       </c>
@@ -2926,7 +2938,7 @@
         <v>304</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>305</v>
@@ -2938,7 +2950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
         <v>306</v>
       </c>
@@ -2949,15 +2961,38 @@
         <v>308</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>309</v>
       </c>
       <c r="F72" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="B73" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>15</v>
       </c>
     </row>
